--- a/data_extactor/batch_10_fa/trimmed/batch_0090_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0090_fa_trim.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>مدل‌سازان چوب (Patternmakers, Wood)</t>
+          <t>الگوسازان چوب (Patternmakers, Wood)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | Mastercam computer-aided design and manufacturing software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook</t>
+          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | ریاضیات | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | ریاضیات | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | طراحی | مهندسی و فناوری | مکانیک | ساخت و ساز | تولید و فرآوری</t>
+          <t>ریاضیات | طراحی | مهندسی و فناوری | مکانیک | ساختمان و ساخت‌وساز | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت کنترل | ثبات دست و بازو | دید نزدیک | چابکی انگشتان | مرتب‌سازی اطلاعات | تجسم فضایی</t>
+          <t>مهارت دستی | دقت کنترل | ثبات دست و بازو | بینایی نزدیک | مهارت انگشتان | ترتیب‌دهی اطلاعات | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | نجاران | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | ماشین‌کاران | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌های چوب‌بری به‌جز اره</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار انبارداری خودکار | Computerized numerical control CNC software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word</t>
+          <t>Adobe Acrobat | نرم‌افزار خودکار موجودی | Computerized numerical control CNC software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | چابکی دستی | ثبات دست و بازو | کنترل سرعت | زمان واکنش | حساسیت به مسئله</t>
+          <t>دقت کنترل | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | کنترل نرخ | زمان عکس‌العمل | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>برشکاران دستی | تنظیم‌کنندگان و متصدیان دستگاه‌های برش و اسلایس | کارگران پرداخت و سنگ‌زنی دستی | تغذیه‌کنندگان و متصدیان خطوط تولید ماشین‌آلات | تنظیم‌کنندگان، متصدیان و اپراتورهای فرز و رنده فلز و پلاستیک | سنگ‌زن‌ها و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌های چوب‌بری به‌جز اره</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | زمان واکنش | دقت کنترل | چابکی دستی | حساسیت به مسئله | هماهنگی چند اندام | چابکی انگشتان</t>
+          <t>بینایی نزدیک | زمان عکس‌العمل | دقت کنترل | مهارت دستی | حساسیت به مسئله | هماهنگی چند عضو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>برشکاران دستی | تنظیم‌کنندگان و متصدیان ماشین‌آلات دریل و حفاری فلز و پلاستیک | کارگران پرداخت و سنگ‌زنی دستی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان خطوط تولید ماشین‌آلات | تنظیم‌کنندگان، متصدیان و اپراتورهای فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | ساخت و ساز | شیمی</t>
+          <t>تولید و فرآوری | مکانیک | طراحی | ریاضیات | زبان انگلیسی | ساختمان و ساخت‌وساز | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چند اندام | دقت کنترل | استحکام ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | رنگ‌کاران و پرداخت‌کاران مبلمان | مدل‌سازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌های چوب‌بری به‌جز اره | نجاران | رویه‌کوبان مبل</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | مدل‌سازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره | نجاران و درودگران | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | سرعت ادراک | استدلال قیاسی | توجه انتخابی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | سرعت ادراکی | استدلال قیاسی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | متصدیان پالایشگاه و فرآیندهای شیمیایی | مهندسان هسته‌ای | تکنسین‌های پایش پرتوی هسته‌ای | تکنسین‌های هسته‌ای | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق</t>
+          <t>مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | تکنسین‌های هسته‌ای | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مخابرات و ارتباطات | مهندسی و فناوری | فیزیک</t>
+          <t>ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مخابرات | مهندسی و فناوری | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان برق | کاردان‌ها و تکنسین‌های فنی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی صنعتی | تعمیرکاران ترانسفورماتور و رله نیروگاهی و پست‌های برق | تکنسین‌های نیروگاه‌های برقابی | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
+          <t>مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | تکنسین‌های نیروگاه برقابی | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | دید نزدیک | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان پالایشگاه و فرآیندهای شیمیایی | اپراتورهای ایستگاه تقویت فشار و کمپرسور گاز | متصدیان تأسیسات گاز | تکنسین‌های نیروگاه‌های برقابی | توزیع‌کنندگان و دیسپچرهای شبکه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | متصدیان تصفیه‌خانه و شبکه‌های آب و فاضلاب</t>
+          <t>اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های نیروگاه برقابی | دیسپچرها و توزیع‌کنندگان شبکه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | سخن گفتن | نگارش | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | شیمی | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>مکانیک | شیمی | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی | استدلال قیاسی | سرعت ادراک</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | استدلال قیاسی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | متصدیان و اپراتورهای تجهیزات شیمیایی | متصدیان پالایشگاه و فرآیندهای شیمیایی | متصدیان تأسیسات گاز | متصدیان پمپاژ و تجهیزات پالایشگاه نفت | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
+          <t>مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش</t>
+          <t>تفکر انتقادی | نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | دقت کنترل | درک شفاهی | استدلال قیاسی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | دقت کنترل | درک شفاهی | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران کنترل‌ها و شیرهای صنعتی | تعمیرکاران ترانسفورماتور و رله نیروگاهی و پست‌های برق | مدیران تولید نیروگاه برقابی | کارگران عمومی تعمیر و نگهداری | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
+          <t>نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مدیران تولید نیروگاه‌های برق‌آبی | کارگران عمومی تعمیرات و نگهداری تاسیسات | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | توجه شنوایی | دقت کنترل</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه شنیداری | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | نصابان و تعمیرکاران کنترل‌ها و شیرهای صنعتی | اپراتورهای ایستگاه تقویت فشار و کمپرسور گاز | مکانیک‌ها و نصابان سیستم‌های سرمایش، گرمایش و تهویه مطبوع | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کشان و تأسیسات‌کاران صنعتی | اپراتورهای نیروگاه برق</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اپراتورهای نیروگاه برق</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
